--- a/feedback_forms/041_weight_loss_program_feedback--feedback_forms.xlsx
+++ b/feedback_forms/041_weight_loss_program_feedback--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'2_weeks'}</t>
+          <t>2_weeks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '2 weeks'}</t>
+          <t>2 weeks</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'4_weeks'}</t>
+          <t>4_weeks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '4 weeks'}</t>
+          <t>4 weeks</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'6_weeks'}</t>
+          <t>6_weeks</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '6 weeks'}</t>
+          <t>6 weeks</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'8_weeks'}</t>
+          <t>8_weeks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '8 weeks'}</t>
+          <t>8 weeks</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'12_weeks'}</t>
+          <t>12_weeks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '12 weeks'}</t>
+          <t>12 weeks</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'online',_'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Online', 'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'in-person',_'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'In-person', 'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'virtual',_'label':_'virtual'}</t>
+          <t>virtual</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Virtual', 'label': 'Virtual'}</t>
+          <t>Virtual</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': '1/5'}</t>
+          <t>1/5</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': '2/5'}</t>
+          <t>2/5</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '3/5'}</t>
+          <t>3/5</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '4/5'}</t>
+          <t>4/5</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '5/5'}</t>
+          <t>5/5</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'lack_of_time'}</t>
+          <t>lack_of_time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Lack of time'}</t>
+          <t>Lack of time</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'cost_was_too_high'}</t>
+          <t>cost_was_too_high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Cost was too high'}</t>
+          <t>Cost was too high</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'program_was_too_difficult'}</t>
+          <t>program_was_too_difficult</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Program was too difficult'}</t>
+          <t>Program was too difficult</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'too_many_commitments'}</t>
+          <t>too_many_commitments</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Too many commitments'}</t>
+          <t>Too many commitments</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'other_(please_specify_in_the_box_below)'}</t>
+          <t>other_(please_specify_in_the_box_below)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Other (please specify in the box below)'}</t>
+          <t>Other (please specify in the box below)</t>
         </is>
       </c>
     </row>
